--- a/3_xgboost/2_datos/1_raw/6_columnas_dataset_rezago_meteo.xlsx
+++ b/3_xgboost/2_datos/1_raw/6_columnas_dataset_rezago_meteo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marco\Documentos\investigacion\machine_learning_idalina\3_xgboost\2_datos\1_raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A31B3CAF-83AE-4C73-AAF2-7E00ABE8CA5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C20FD455-5445-4210-960A-F07CC919CC61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
   <si>
     <t>columnas</t>
   </si>
@@ -28,9 +28,6 @@
     <t>fecha</t>
   </si>
   <si>
-    <t>año</t>
-  </si>
-  <si>
     <t>semana_epi</t>
   </si>
   <si>
@@ -55,21 +52,6 @@
     <t>dias_lluvia</t>
   </si>
   <si>
-    <t>vel_vi</t>
-  </si>
-  <si>
-    <t>vel_vi_max</t>
-  </si>
-  <si>
-    <t>vel_vi_min</t>
-  </si>
-  <si>
-    <t>soi</t>
-  </si>
-  <si>
-    <t>sst</t>
-  </si>
-  <si>
     <t>casos_dengue</t>
   </si>
   <si>
@@ -325,135 +307,6 @@
     <t>dias_lluvia_lag_12</t>
   </si>
   <si>
-    <t>vel_vi_lag_1</t>
-  </si>
-  <si>
-    <t>vel_vi_lag_2</t>
-  </si>
-  <si>
-    <t>vel_vi_lag_3</t>
-  </si>
-  <si>
-    <t>vel_vi_lag_4</t>
-  </si>
-  <si>
-    <t>vel_vi_lag_5</t>
-  </si>
-  <si>
-    <t>vel_vi_lag_6</t>
-  </si>
-  <si>
-    <t>vel_vi_lag_7</t>
-  </si>
-  <si>
-    <t>vel_vi_lag_8</t>
-  </si>
-  <si>
-    <t>vel_vi_lag_9</t>
-  </si>
-  <si>
-    <t>vel_vi_lag_10</t>
-  </si>
-  <si>
-    <t>vel_vi_lag_11</t>
-  </si>
-  <si>
-    <t>vel_vi_lag_12</t>
-  </si>
-  <si>
-    <t>vel_vi_max_lag_1</t>
-  </si>
-  <si>
-    <t>vel_vi_max_lag_2</t>
-  </si>
-  <si>
-    <t>vel_vi_max_lag_3</t>
-  </si>
-  <si>
-    <t>vel_vi_max_lag_4</t>
-  </si>
-  <si>
-    <t>vel_vi_max_lag_5</t>
-  </si>
-  <si>
-    <t>vel_vi_max_lag_6</t>
-  </si>
-  <si>
-    <t>vel_vi_max_lag_7</t>
-  </si>
-  <si>
-    <t>vel_vi_max_lag_8</t>
-  </si>
-  <si>
-    <t>vel_vi_max_lag_9</t>
-  </si>
-  <si>
-    <t>vel_vi_max_lag_10</t>
-  </si>
-  <si>
-    <t>vel_vi_max_lag_11</t>
-  </si>
-  <si>
-    <t>vel_vi_max_lag_12</t>
-  </si>
-  <si>
-    <t>vel_vi_min_lag_1</t>
-  </si>
-  <si>
-    <t>vel_vi_min_lag_2</t>
-  </si>
-  <si>
-    <t>vel_vi_min_lag_3</t>
-  </si>
-  <si>
-    <t>vel_vi_min_lag_4</t>
-  </si>
-  <si>
-    <t>vel_vi_min_lag_5</t>
-  </si>
-  <si>
-    <t>vel_vi_min_lag_6</t>
-  </si>
-  <si>
-    <t>vel_vi_min_lag_7</t>
-  </si>
-  <si>
-    <t>vel_vi_min_lag_8</t>
-  </si>
-  <si>
-    <t>vel_vi_min_lag_9</t>
-  </si>
-  <si>
-    <t>vel_vi_min_lag_10</t>
-  </si>
-  <si>
-    <t>vel_vi_min_lag_11</t>
-  </si>
-  <si>
-    <t>vel_vi_min_lag_12</t>
-  </si>
-  <si>
-    <t>soi_lag_1</t>
-  </si>
-  <si>
-    <t>soi_lag_2</t>
-  </si>
-  <si>
-    <t>soi_lag_3</t>
-  </si>
-  <si>
-    <t>soi_lag_4</t>
-  </si>
-  <si>
-    <t>soi_lag_5</t>
-  </si>
-  <si>
-    <t>soi_lag_6</t>
-  </si>
-  <si>
-    <t>soi_lag_7</t>
-  </si>
-  <si>
     <t>soi_lag_8</t>
   </si>
   <si>
@@ -467,27 +320,6 @@
   </si>
   <si>
     <t>soi_lag_12</t>
-  </si>
-  <si>
-    <t>sst_lag_1</t>
-  </si>
-  <si>
-    <t>sst_lag_2</t>
-  </si>
-  <si>
-    <t>sst_lag_3</t>
-  </si>
-  <si>
-    <t>sst_lag_4</t>
-  </si>
-  <si>
-    <t>sst_lag_5</t>
-  </si>
-  <si>
-    <t>sst_lag_6</t>
-  </si>
-  <si>
-    <t>sst_lag_7</t>
   </si>
   <si>
     <t>sst_lag_8</t>
@@ -842,7 +674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A161"/>
+  <dimension ref="A1:A105"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -897,32 +729,32 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
@@ -1367,287 +1199,7 @@
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A106" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A107" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A108" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A109" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A110" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A111" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A112" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A113" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A114" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A115" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A116" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A117" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A118" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A119" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A120" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A121" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A122" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A123" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A124" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A125" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A126" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A127" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A128" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A129" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A130" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A131" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A132" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A133" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A134" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A135" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A136" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A137" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A138" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A139" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A140" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A141" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A142" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A143" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A144" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A145" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A146" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A147" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A148" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A149" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A150" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A151" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A152" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A153" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A154" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A155" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A156" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A157" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A158" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A159" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A160" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A161" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
